--- a/data/trans_dic/P57B3_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P57B3_R-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,07</t>
+          <t>0,43; 2,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,71</t>
+          <t>0,78; 2,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,26</t>
+          <t>0,84; 2,43</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 10,71</t>
+          <t>5,39; 10,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,94; 12,76</t>
+          <t>8,05; 12,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,08; 10,82</t>
+          <t>7,2; 10,75</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,83; 14,2</t>
+          <t>8,26; 14,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,88; 16,38</t>
+          <t>11,57; 17,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,18; 14,51</t>
+          <t>10,87; 15,15</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 9,14</t>
+          <t>2,9; 8,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 9,5</t>
+          <t>6,54; 12,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 8,37</t>
+          <t>5,32; 9,19</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,45; 19,23</t>
+          <t>11,11; 20,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,56; 14,26</t>
+          <t>9,29; 15,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,44; 15,7</t>
+          <t>11,09; 16,05</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,96; 19,0</t>
+          <t>12,53; 20,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,08; 16,3</t>
+          <t>11,22; 17,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,18; 16,8</t>
+          <t>13,08; 17,89</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,04; 10,52</t>
+          <t>6,57; 10,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,33; 10,25</t>
+          <t>7,75; 12,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,47; 9,26</t>
+          <t>7,8; 10,64</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,52; 73,6</t>
+          <t>20,07; 26,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,44; 28,93</t>
+          <t>23,82; 29,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23,64; 59,61</t>
+          <t>22,71; 26,73</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,97; 37,04</t>
+          <t>10,71; 13,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,8; 13,21</t>
+          <t>12,62; 14,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,54; 26,32</t>
+          <t>12,02; 13,44</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>9174</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1122; 9576</t>
+          <t>1368; 9192</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2139; 7835</t>
+          <t>2471; 9056</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4528; 13555</t>
+          <t>5306; 15408</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>39733</t>
+          <t>40884</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51849</t>
+          <t>55387</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91582</t>
+          <t>96271</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26314; 55433</t>
+          <t>28547; 56848</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40812; 65589</t>
+          <t>43899; 70108</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73034; 111617</t>
+          <t>77452; 115519</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33633</t>
+          <t>35420</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47022</t>
+          <t>51024</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80656</t>
+          <t>86444</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24747; 44876</t>
+          <t>26117; 46282</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37992; 57184</t>
+          <t>41237; 61433</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67717; 96498</t>
+          <t>73059; 101893</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>17463</t>
+          <t>18649</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31237</t>
+          <t>36052</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48699</t>
+          <t>54701</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10161; 28562</t>
+          <t>10823; 30590</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17836; 45036</t>
+          <t>27495; 50439</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33297; 65849</t>
+          <t>42203; 72874</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25641</t>
+          <t>31043</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23576</t>
+          <t>26613</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49217</t>
+          <t>57656</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18687; 34363</t>
+          <t>22839; 41381</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17830; 29697</t>
+          <t>21063; 34308</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40406; 60753</t>
+          <t>47949; 69435</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>40916</t>
+          <t>43576</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>34510</t>
+          <t>36700</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75426</t>
+          <t>80276</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>32255; 51240</t>
+          <t>33924; 54244</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28474; 41904</t>
+          <t>29580; 45384</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>64166; 88483</t>
+          <t>69917; 95638</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>61387</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>61185</t>
+          <t>74438</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>111014</t>
+          <t>135825</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>37709; 65654</t>
+          <t>47300; 78974</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28185; 86742</t>
+          <t>59649; 92297</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>65685; 136134</t>
+          <t>116178; 158430</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>398375</t>
+          <t>181919</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>186487</t>
+          <t>219580</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>584863</t>
+          <t>401499</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>199678; 682821</t>
+          <t>159947; 207710</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>168202; 207670</t>
+          <t>198017; 243292</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>388937; 980872</t>
+          <t>369757; 435253</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>609334</t>
+          <t>417039</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>440490</t>
+          <t>504807</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1049824</t>
+          <t>921846</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>379463; 1280857</t>
+          <t>378278; 460031</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>358236; 482937</t>
+          <t>470570; 542857</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>820712; 1872786</t>
+          <t>872490; 975451</t>
         </is>
       </c>
     </row>
